--- a/Luban/Datas/Missile.xlsx
+++ b/Luban/Datas/Missile.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missile" sheetId="1" r:id="R808ef7e12567434c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missile" sheetId="1" r:id="R2729dc2c00184e17"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -97,7 +97,7 @@
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="8">
+  <x:cellXfs count="9">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
@@ -118,6 +118,14 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="3">
     <x:cellStyle name="常规" xfId="0"/>
@@ -195,6 +203,23 @@
 </x:styleSheet>
 </file>
 
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<xfpb:FeaturePropertyBags xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <xfpb:bag type="Checkbox"/>
+  <xfpb:bag type="XFControls">
+    <xfpb:bagId k="CellControl">0</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplement">
+    <xfpb:bagId k="XFControls">1</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <xfpb:a k="MappedFeaturePropertyBags">
+      <xfpb:bagId>2</xfpb:bagId>
+    </xfpb:a>
+  </xfpb:bag>
+</xfpb:FeaturePropertyBags>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
@@ -238,9 +263,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -2328,6 +2353,118 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
+    <x:row r="13">
+      <x:c r="A13"/>
+      <x:c r="B13" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>missile_fast_homing_1201</x:v>
+      </x:c>
+      <x:c r="D13" t="n">
+        <x:v>1201</x:v>
+      </x:c>
+      <x:c r="E13" t="str">
+        <x:v>高速追踪导弹</x:v>
+      </x:c>
+      <x:c r="F13" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G13" t="n">
+        <x:v>4.2</x:v>
+      </x:c>
+      <x:c r="H13" t="n">
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="I13" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="J13" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L13" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="M13" t="n">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="N13" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="O13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V13" t="str"/>
+      <x:c r="W13" s="8" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y13" s="8" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z13" t="str">
+        <x:v>Assets/Prefabs/Missiles/missile_03_weak_homing.prefab</x:v>
+      </x:c>
+      <x:c r="AA13" t="str">
+        <x:v>Assets/Art/Sprites/Bullets/missile_03.png</x:v>
+      </x:c>
+      <x:c r="AB13" t="str"/>
+      <x:c r="AC13" t="str">
+        <x:v>contrail</x:v>
+      </x:c>
+      <x:c r="AD13" t="str"/>
+      <x:c r="AE13" t="str">
+        <x:v>#FFE45C</x:v>
+      </x:c>
+      <x:c r="AF13" t="str"/>
+      <x:c r="AG13" t="str"/>
+      <x:c r="AH13" t="str"/>
+      <x:c r="AI13" t="str"/>
+      <x:c r="AJ13" t="str"/>
+      <x:c r="AK13" t="str"/>
+      <x:c r="AL13" t="str"/>
+      <x:c r="AM13" t="str"/>
+      <x:c r="AN13" t="str"/>
+      <x:c r="AO13" t="str"/>
+      <x:c r="AP13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AQ13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AR13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AS13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AT13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
